--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_VK.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_VK.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R7d5cf45854db4733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R8c3f3cee216e4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rb5edabc508114a07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R8c99135b7d214f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R2c9dbb76adb54a6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R96f83eb6896744d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R670285aa25c34b94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R56280903bba14619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R4e73b6a414774e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R0b7d389ffa224fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rf75d0dae425e4ca6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R4a339a12a6bb4b96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R2eae6c96739347ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R5539e81257274708"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Re0d05c080a47408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R33ad33b59b544769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rdbf2cefaee384e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R1a242e8a2fdb4f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rc328ca272de2432c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Reb623e52244b46df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R2e6ac2d0a9624434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R3d9c42e3299a4fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rb0bc03e3036943c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rad4159f5def34f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R0a3c53f362c4407a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rbbd68dc90790458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Re90d5d6dc24b4d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R82ac229425bc4538"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R0d8d4478a1f54fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R76610c6bd6034712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Ra8b706148c6e41c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R94e948100ad14ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Re743bf1e0e374b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rb1e93af172e7411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R3d35fa9552de436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rc03a45ec3f9f4d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R0c981008395845ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7657c0d14c4f4c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R169a50b7a89f46c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R2de42acc0ea442b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rd7b2a5896c24442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R548931aa47c04b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R79f71d0d2a4346c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3445,6 +3446,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ソフィア・エーデルヴァイス</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>カルフェオン神聖大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
